--- a/artfynd/A 11261-2026 artfynd.xlsx
+++ b/artfynd/A 11261-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131540837</v>
       </c>
       <c r="B2" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131540827</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
